--- a/ksoft_old/_bakas/Papeis IP.xlsx
+++ b/ksoft_old/_bakas/Papeis IP.xlsx
@@ -2034,13 +2034,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13EBB7D-A382-4B7F-982D-EC6EA2B2498E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A13BA53A-24E6-4870-8FE8-4C0E0EFFE777}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9DF7EE7-3961-4948-8D9B-BA70D2699D7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B2E1697-0F17-4A75-9F39-A2CC839F991B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AAB6382-C7C3-467E-8297-0556DEEC5987}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A832507-AF71-443D-A724-68E528D67ED5}"/>
 </file>
--- a/ksoft_old/_bakas/Papeis IP.xlsx
+++ b/ksoft_old/_bakas/Papeis IP.xlsx
@@ -2034,13 +2034,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A13BA53A-24E6-4870-8FE8-4C0E0EFFE777}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7C672C6-F104-4186-B0BE-54823227528C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B2E1697-0F17-4A75-9F39-A2CC839F991B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1AE2A0-11FF-4818-ACD4-961C8D7D51E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A832507-AF71-443D-A724-68E528D67ED5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B96ECFCF-660E-4D63-A532-D984D3C0235C}"/>
 </file>
--- a/ksoft_old/_bakas/Papeis IP.xlsx
+++ b/ksoft_old/_bakas/Papeis IP.xlsx
@@ -2034,13 +2034,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7C672C6-F104-4186-B0BE-54823227528C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13EBB7D-A382-4B7F-982D-EC6EA2B2498E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1AE2A0-11FF-4818-ACD4-961C8D7D51E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9DF7EE7-3961-4948-8D9B-BA70D2699D7F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B96ECFCF-660E-4D63-A532-D984D3C0235C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AAB6382-C7C3-467E-8297-0556DEEC5987}"/>
 </file>